--- a/ornek-takimlar/kartal-sigorta.xlsx
+++ b/ornek-takimlar/kartal-sigorta.xlsx
@@ -8,14 +8,10 @@
     <sheet name="Input" sheetId="1" r:id="rId1"/>
     <sheet name="Premium" sheetId="2" r:id="rId2"/>
     <sheet name="Marketing" sheetId="3" r:id="rId3"/>
-    <sheet name="Claim" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="CoefficientList">Premium!$XFD$1:$XFD$41</definedName>
-    <definedName name="FocusList">Marketing!$XFC$1:$XFC$19</definedName>
-    <definedName name="OfferList">Marketing!$XFD$1:$XFD$4</definedName>
     <definedName name="PercentageList">Marketing!$XFB$1:$XFB$21</definedName>
-    <definedName name="YesNoList">Claim!$XFD$1:$XFD$2</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -155,7 +151,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -318,40 +314,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF004894"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF004894"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF004894"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF004894"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -444,7 +411,7 @@
     <xf numFmtId="9" fontId="8" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -460,63 +427,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -600,27 +510,11 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pazarlama bütçesini ve kanal dağılımını belirle (her kanal en az %10, toplam = %100) ve dijital kampanyayı kur</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="24.8" customHeight="1">
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3️⃣</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HASAR</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hasar operasyonu bütçesini belirle ve kota paylı reasüransı seç</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">Pazarlama bütçesini belirle, medya ve hediye arasında böl (toplam = %100) ve hediyeleri ağırlıklandır (toplam = %100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24.8" customHeight="1"/>
     <row r="11" ht="30" customHeight="1">
       <c r="B11" s="7" t="inlineStr">
         <is>
@@ -648,7 +542,7 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pazarlama kanallarının toplamı %100 olmalı; medya + hediye %100 olmalı.</t>
+          <t xml:space="preserve">Medya + hediye %100 olmalı; hediye ağırlıkları %100 olmalı.</t>
         </is>
       </c>
     </row>
@@ -660,7 +554,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pazarlama + hasar operasyonu + reasürans bedeli karar bütçesini (€1.022.000) aşmamalı.</t>
+          <t xml:space="preserve">Pazarlama bütçesi €1.022.000 tutarını aşmamalı.</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1121,7 @@
     <col min="7" max="7" width="31.9" customWidth="1"/>
     <col min="9" max="9" width="10.3" customWidth="1"/>
     <col min="10" max="10" width="8.1" customWidth="1"/>
-    <col min="11" max="11" width="16.1" customWidth="1"/>
+    <col min="11" max="11" width="12.6" customWidth="1"/>
     <col min="12" max="12" width="11.3" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1235,64 +1129,32 @@
       <c r="XFB1" s="23">
         <v>0</v>
       </c>
-      <c r="XFC1" s="23">
-        <v>0.1</v>
-      </c>
-      <c r="XFD1" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Konser / etkinlik indirimi</t>
-        </is>
-      </c>
     </row>
     <row r="2" ht="35.2" customHeight="1">
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAZARLAMA - KANAL DAĞILIMI</t>
+          <t xml:space="preserve">PAZARLAMA - MEDYA VE HEDİYE</t>
         </is>
       </c>
       <c r="XFB2" s="23">
         <v>0.05</v>
       </c>
-      <c r="XFC2" s="23">
-        <v>0.15</v>
-      </c>
-      <c r="XFD2" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Restoran hediye kartı</t>
-        </is>
-      </c>
     </row>
     <row r="3" ht="37.2" customHeight="1">
       <c r="B3" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pazarlama bütçen satış kanallarında görünürlük alır ve dijital kampanya yürütebilir.
-Kampanyayı medya ve hediye arasında böl. Toplam %100 olmalı.</t>
+          <t xml:space="preserve">En fazla €1.022.000 bütçen var. Bunu medya ve hediye arasında böleceksin.
+Toplam %100 olmalı. Sonra hediyeleri ağırlıklandır: onların toplamı da %100 olmalı.</t>
         </is>
       </c>
       <c r="XFB3" s="23">
         <v>0.1</v>
-      </c>
-      <c r="XFC3" s="23">
-        <v>0.2</v>
-      </c>
-      <c r="XFD3" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kahve hediye kartı</t>
-        </is>
       </c>
     </row>
     <row r="4">
       <c r="XFB4" s="23">
         <v>0.15</v>
       </c>
-      <c r="XFC4" s="23">
-        <v>0.25</v>
-      </c>
-      <c r="XFD4" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Spor salonu üyelik indirimi</t>
-        </is>
-      </c>
     </row>
     <row r="5" ht="42.6" customHeight="1">
       <c r="B5" s="25" t="inlineStr">
@@ -1305,41 +1167,26 @@
       <c r="XFB5" s="23">
         <v>0.2</v>
       </c>
-      <c r="XFC5" s="23">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="6">
       <c r="XFB6" s="23">
         <v>0.25</v>
       </c>
-      <c r="XFC6" s="23">
-        <v>0.35</v>
-      </c>
     </row>
     <row r="7">
       <c r="XFB7" s="23">
         <v>0.3</v>
       </c>
-      <c r="XFC7" s="23">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="8">
       <c r="XFB8" s="23">
         <v>0.35</v>
       </c>
-      <c r="XFC8" s="23">
-        <v>0.45</v>
-      </c>
     </row>
     <row r="9">
       <c r="XFB9" s="23">
         <v>0.4</v>
       </c>
-      <c r="XFC9" s="23">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="10" ht="27.8" customHeight="1">
       <c r="B10" s="26" t="inlineStr">
@@ -1375,9 +1222,6 @@
       <c r="XFB10" s="23">
         <v>0.45</v>
       </c>
-      <c r="XFC10" s="23">
-        <v>0.55</v>
-      </c>
     </row>
     <row r="11" ht="27.8" customHeight="1">
       <c r="B11" s="27" t="inlineStr">
@@ -1408,9 +1252,6 @@
       </c>
       <c r="XFB11" s="23">
         <v>0.5</v>
-      </c>
-      <c r="XFC11" s="23">
-        <v>0.6</v>
       </c>
     </row>
     <row r="12" ht="27.8" customHeight="1">
@@ -1437,9 +1278,6 @@
       <c r="XFB12" s="23">
         <v>0.55</v>
       </c>
-      <c r="XFC12" s="23">
-        <v>0.65</v>
-      </c>
     </row>
     <row r="13" ht="29.2" customHeight="1">
       <c r="B13" s="30" t="inlineStr">
@@ -1454,19 +1292,20 @@
       <c r="XFB13" s="23">
         <v>0.6</v>
       </c>
-      <c r="XFC13" s="23">
-        <v>0.7</v>
-      </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="B14" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">KAMPANYA BÜTÇESİ</t>
-        </is>
-      </c>
-      <c r="C14" s="30"/>
+          <t xml:space="preserve">BÜTÇE</t>
+        </is>
+      </c>
+      <c r="C14" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yıllık pazarlaman (en fazla €1.022.000)</t>
+        </is>
+      </c>
       <c r="D14" s="32">
-        <f>D23*D24</f>
+        <v>409000</v>
       </c>
       <c r="F14" s="34" t="inlineStr">
         <is>
@@ -1477,12 +1316,10 @@
       <c r="H14" s="34"/>
       <c r="I14" s="34"/>
       <c r="J14" s="34"/>
+      <c r="K14" s="34"/>
       <c r="XFB14" s="23">
         <v>0.65</v>
       </c>
-      <c r="XFC14" s="23">
-        <v>0.75</v>
-      </c>
     </row>
     <row r="15">
       <c r="F15" s="34" t="inlineStr">
@@ -1510,14 +1347,24 @@
           <t xml:space="preserve">Hit oranı</t>
         </is>
       </c>
+      <c r="K15" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ağırlık</t>
+        </is>
+      </c>
       <c r="XFB15" s="23">
         <v>0.7</v>
       </c>
-      <c r="XFC15" s="23">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="16">
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hediye başına müşteri = erişim × ağırlık × ilgi × tıklama × hit oranı.
+Her hediye en fazla (hediye bütçesi × ağırlığı) ÷ maliyeti kadar müşteriye yeter.</t>
+        </is>
+      </c>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
       <c r="F16" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">Konser / etkinlik indirimi</t>
@@ -1535,14 +1382,17 @@
       <c r="J16" s="36">
         <v>0.1</v>
       </c>
+      <c r="K16" s="29">
+        <v>0</v>
+      </c>
       <c r="XFB16" s="23">
         <v>0.75</v>
       </c>
-      <c r="XFC16" s="23">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="17">
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
       <c r="F17" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">Restoran hediye kartı</t>
@@ -1560,14 +1410,14 @@
       <c r="J17" s="36">
         <v>0.07</v>
       </c>
+      <c r="K17" s="29">
+        <v>0.2</v>
+      </c>
       <c r="XFB17" s="23">
         <v>0.8</v>
       </c>
-      <c r="XFC17" s="23">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="18">
+    </row>
+    <row r="18" ht="24" customHeight="1">
       <c r="F18" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">Kahve hediye kartı</t>
@@ -1585,12 +1435,12 @@
       <c r="J18" s="36">
         <v>0.09</v>
       </c>
+      <c r="K18" s="29">
+        <v>0</v>
+      </c>
       <c r="XFB18" s="23">
         <v>0.85</v>
       </c>
-      <c r="XFC18" s="23">
-        <v>0.95</v>
-      </c>
     </row>
     <row r="19" ht="14.4" customHeight="1">
       <c r="F19" s="35" t="inlineStr">
@@ -1610,11 +1460,11 @@
       <c r="J19" s="36">
         <v>0.15</v>
       </c>
+      <c r="K19" s="29">
+        <v>0.8</v>
+      </c>
       <c r="XFB19" s="23">
         <v>0.9</v>
-      </c>
-      <c r="XFC19" s="23">
-        <v>1</v>
       </c>
     </row>
     <row r="20" ht="27.6" customHeight="1">
@@ -1627,6 +1477,9 @@
       <c r="H20" s="24"/>
       <c r="I20" s="24"/>
       <c r="J20" s="24"/>
+      <c r="K20" s="31">
+        <f>SUM(K16:K19)</f>
+      </c>
       <c r="XFB20" s="23">
         <v>0.95</v>
       </c>
@@ -1636,396 +1489,40 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" ht="27.8" customHeight="1">
-      <c r="B22" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pazarlama</t>
-        </is>
-      </c>
-      <c r="C22" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Açıklama</t>
-        </is>
-      </c>
-      <c r="D22" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Değer</t>
-        </is>
-      </c>
-      <c r="F22" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SEÇİLEN HEDİYE</t>
-        </is>
-      </c>
-      <c r="G22" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Spor salonu üyelik indirimi</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="24.8" customHeight="1">
-      <c r="B23" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bütçe</t>
-        </is>
-      </c>
-      <c r="C23" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Yıllık toplam pazarlama; karar bütçesinden</t>
-        </is>
-      </c>
-      <c r="D23" s="39">
-        <v>409000</v>
-      </c>
-    </row>
-    <row r="24" ht="24.8" customHeight="1">
-      <c r="B24" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kampanya payı</t>
-        </is>
-      </c>
-      <c r="C24" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dijital kampanyaya gider; kalanı kanal görünürlüğü alır</t>
-        </is>
-      </c>
-      <c r="D24" s="29">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="26" ht="27.8" customHeight="1">
-      <c r="B26" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kanal</t>
-        </is>
-      </c>
-      <c r="C26" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Açıklama</t>
-        </is>
-      </c>
-      <c r="D26" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pay</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="21.8" customHeight="1">
-      <c r="B27" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agency</t>
-        </is>
-      </c>
-      <c r="C27" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Acente pazarlama desteği</t>
-        </is>
-      </c>
-      <c r="D27" s="29">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="28" ht="21.8" customHeight="1">
-      <c r="B28" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bank</t>
-        </is>
-      </c>
-      <c r="C28" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bankasürans görünürlüğü</t>
-        </is>
-      </c>
-      <c r="D28" s="29">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="29" ht="21.8" customHeight="1">
-      <c r="B29" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Digital</t>
-        </is>
-      </c>
-      <c r="C29" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Çevrimiçi görünürlük (kampanya dışında)</t>
-        </is>
-      </c>
-      <c r="D29" s="29">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="30" ht="21.8" customHeight="1">
-      <c r="B30" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Broker</t>
-        </is>
-      </c>
-      <c r="C30" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Broker desteği</t>
-        </is>
-      </c>
-      <c r="D30" s="29">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="31" ht="27.8" customHeight="1">
-      <c r="B31" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TOTAL</t>
-        </is>
-      </c>
-      <c r="C31" s="30"/>
-      <c r="D31" s="31">
-        <f>SUM(D27:D30)</f>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="B5:H5"/>
     <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B16:D17"/>
     <mergeCell ref="F12:H12"/>
-    <mergeCell ref="F14:J14"/>
+    <mergeCell ref="F14:K14"/>
     <mergeCell ref="F20:J20"/>
-    <mergeCell ref="B31:C31"/>
   </mergeCells>
   <conditionalFormatting sqref="D13">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="notEqual">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D31">
+  <conditionalFormatting sqref="K20">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="notEqual">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="Listeden bir pay seç (%5 adım)." sqref="D11:D12 D24">
+  <conditionalFormatting sqref="D14">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
+      <formula>1022000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="Listeden bir pay seç (%5 adım)." sqref="D11:D12 K16:K19">
       <formula1>PercentageList</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="Listeden bir pay seç (en az %10)." sqref="D27:D30">
-      <formula1>FocusList</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="Hediyelerden birini seç." sqref="G22">
-      <formula1>OfferList</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showErrorMessage="1" error="0 ile 1022000 arasında gir." sqref="D23">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showErrorMessage="1" error="0 ile 1022000 arasında gir." sqref="D14">
       <formula1>0</formula1>
       <formula2>1022000</formula2>
     </dataValidation>
   </dataValidations>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <tabColor rgb="FF004894"/>
-  </sheetPr>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="3.9" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="45.4" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="11" max="11" width="4.9" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="XFD1" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Evet</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="35.2" customHeight="1">
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HASAR - BÜTÇE DAĞILIMI</t>
-        </is>
-      </c>
-      <c r="XFD2" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hayır</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24.8" customHeight="1">
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hasar operasyonu bütçesini ve reasürans anlaşmasını belirle</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="27.8" customHeight="1">
-      <c r="B5" s="40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">📊 HASAR OPERASYONU</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="26.2" customHeight="1">
-      <c r="B7" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PARAMETRE</t>
-        </is>
-      </c>
-      <c r="C7" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AÇIKLAMA</t>
-        </is>
-      </c>
-      <c r="D7" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DEĞER</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="26.2" customHeight="1">
-      <c r="B8" s="44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hasar operasyonu</t>
-        </is>
-      </c>
-      <c r="C8" s="45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hasar yönetim kapasitesi. Az olursa memnuniyet (NPS) düşer, hasar maliyeti kaçar.</t>
-        </is>
-      </c>
-      <c r="D8" s="46">
-        <v>460000</v>
-      </c>
-    </row>
-    <row r="9" ht="26.2" customHeight="1">
-      <c r="B9" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pazarlama bütçesi</t>
-        </is>
-      </c>
-      <c r="C9" s="48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pazarlama sayfasından</t>
-        </is>
-      </c>
-      <c r="D9" s="49">
-        <f>Marketing!D23</f>
-      </c>
-    </row>
-    <row r="10" ht="26.2" customHeight="1">
-      <c r="B10" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reasürans bedeli</t>
-        </is>
-      </c>
-      <c r="C10" s="48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Anlaşma seçilirse bütçeden ödenir</t>
-        </is>
-      </c>
-      <c r="D10" s="49">
-        <f>IF(D17="Evet",128000,0)</f>
-      </c>
-    </row>
-    <row r="11" ht="26.2" customHeight="1">
-      <c r="B11" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Karar bütçesi</t>
-        </is>
-      </c>
-      <c r="C11" s="48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Yıl içinde harcayabileceğin en fazla tutar</t>
-        </is>
-      </c>
-      <c r="D11" s="49">
-        <v>1022000</v>
-      </c>
-    </row>
-    <row r="12" ht="27.8" customHeight="1">
-      <c r="B12" s="50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TOPLAM KULLANILAN</t>
-        </is>
-      </c>
-      <c r="C12" s="51"/>
-      <c r="D12" s="52">
-        <f>D8+D9+D10</f>
-      </c>
-    </row>
-    <row r="14" ht="27.8" customHeight="1">
-      <c r="B14" s="40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">🔄 REASÜRANS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="26.2" customHeight="1">
-      <c r="B16" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PARAMETRE</t>
-        </is>
-      </c>
-      <c r="C16" s="42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AÇIKLAMA</t>
-        </is>
-      </c>
-      <c r="D16" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DEĞER</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="27.8" customHeight="1">
-      <c r="B17" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kota paylı reasürans</t>
-        </is>
-      </c>
-      <c r="C17" s="54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prim ve hasarın %30’ini %25 komisyonla devreder; bedeli €128.000</t>
-        </is>
-      </c>
-      <c r="D17" s="55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Evet</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">💡 Not: Tüm seçimler açılır listelerden yapılır. Toplam kullanılan karar bütçesini aşmamalı; reasürans yıl boyunca geçerlidir.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="B5:I5"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B14:I14"/>
-    <mergeCell ref="B19:I19"/>
-  </mergeCells>
-  <conditionalFormatting sqref="D12">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
-      <formula>D11</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="2">
-    <dataValidation type="decimal" operator="between" allowBlank="1" showErrorMessage="1" error="0 ile 1022000 arasında gir." sqref="D8">
-      <formula1>0</formula1>
-      <formula2>1022000</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="Evet ya da Hayır seç." sqref="D17">
-      <formula1>YesNoList</formula1>
-    </dataValidation>
-  </dataValidations>
-</worksheet>
 </file>
--- a/ornek-takimlar/kartal-sigorta.xlsx
+++ b/ornek-takimlar/kartal-sigorta.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pazarlama bütçesi €1.022.000 tutarını aşmamalı.</t>
+          <t xml:space="preserve">Pazarlama bütçesi €500.000 tutarını aşmamalı.</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
     <row r="3" ht="37.2" customHeight="1">
       <c r="B3" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">En fazla €1.022.000 bütçen var. Bunu medya ve hediye arasında böleceksin.
+          <t xml:space="preserve">En fazla €500.000 bütçen var. Bunu medya ve hediye arasında böleceksin.
 Toplam %100 olmalı. Sonra hediyeleri ağırlıklandır: onların toplamı da %100 olmalı.</t>
         </is>
       </c>
@@ -1301,11 +1301,11 @@
       </c>
       <c r="C14" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yıllık pazarlaman (en fazla €1.022.000)</t>
+          <t xml:space="preserve">Yıllık pazarlaman (en fazla €500.000)</t>
         </is>
       </c>
       <c r="D14" s="32">
-        <v>409000</v>
+        <v>200000</v>
       </c>
       <c r="F14" s="34" t="inlineStr">
         <is>
@@ -1512,16 +1512,16 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
-      <formula>1022000</formula>
+      <formula>500000</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" error="Listeden bir pay seç (%5 adım)." sqref="D11:D12 K16:K19">
       <formula1>PercentageList</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showErrorMessage="1" error="0 ile 1022000 arasında gir." sqref="D14">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showErrorMessage="1" error="0 ile 500000 arasında gir." sqref="D14">
       <formula1>0</formula1>
-      <formula2>1022000</formula2>
+      <formula2>500000</formula2>
     </dataValidation>
   </dataValidations>
 </worksheet>
